--- a/data/trans_camb/MCS12_SP_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,2</t>
+          <t>-6,05; 3,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 5,04</t>
+          <t>-5,24; 4,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 5,81</t>
+          <t>-4,53; 5,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 7,43</t>
+          <t>-6,56; 7,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 2,3</t>
+          <t>-10,06; 2,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 6,24</t>
+          <t>-5,82; 5,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 3,5</t>
+          <t>-4,67; 3,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 2,35</t>
+          <t>-5,7; 2,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,82</t>
+          <t>-2,37; 4,93</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 27,12</t>
+          <t>-30,31; 26,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 33,17</t>
+          <t>-25,99; 33,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 38,62</t>
+          <t>-21,86; 37,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 39,62</t>
+          <t>-25,64; 39,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 11,1</t>
+          <t>-40,09; 13,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 34,48</t>
+          <t>-21,2; 30,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 20,26</t>
+          <t>-21,98; 22,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 14,63</t>
+          <t>-26,44; 16,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 28,25</t>
+          <t>-11,69; 29,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 11,36</t>
+          <t>0,51; 11,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 7,96</t>
+          <t>-3,43; 7,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 6,66</t>
+          <t>-3,96; 6,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 13,85</t>
+          <t>-0,85; 13,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 5,17</t>
+          <t>-8,55; 4,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,17</t>
+          <t>-7,3; 4,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 10,37</t>
+          <t>1,07; 10,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 4,79</t>
+          <t>-3,84; 4,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,7</t>
+          <t>-4,49; 3,37</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 96,39</t>
+          <t>2,51; 100,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 66,57</t>
+          <t>-19,01; 61,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 55,91</t>
+          <t>-22,02; 56,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 60,63</t>
+          <t>-2,96; 58,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 22,23</t>
+          <t>-29,44; 20,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 23,09</t>
+          <t>-25,26; 19,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 56,54</t>
+          <t>4,83; 56,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 26,07</t>
+          <t>-16,89; 26,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 20,16</t>
+          <t>-19,64; 19,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,46</t>
+          <t>2,69; 12,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,58</t>
+          <t>-1,12; 8,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 6,54</t>
+          <t>-14,66; 7,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 18,27</t>
+          <t>0,83; 18,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 16,39</t>
+          <t>-4,07; 16,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 8,06</t>
+          <t>-8,33; 8,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,53</t>
+          <t>3,93; 12,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 8,52</t>
+          <t>-0,49; 8,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 5,53</t>
+          <t>-13,65; 5,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,38; 78,48</t>
+          <t>12,93; 78,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 54,24</t>
+          <t>-6,08; 54,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,59; 37,7</t>
+          <t>-72,55; 41,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 87,81</t>
+          <t>2,88; 92,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 79,19</t>
+          <t>-14,12; 76,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 40,42</t>
+          <t>-26,76; 44,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,39; 71,27</t>
+          <t>17,87; 71,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 49,13</t>
+          <t>-2,15; 48,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,64; 28,88</t>
+          <t>-60,41; 28,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 6,15</t>
+          <t>-1,08; 5,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 1,38</t>
+          <t>-5,32; 1,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,49</t>
+          <t>-4,35; 2,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,13</t>
+          <t>-1,1; 8,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 4,61</t>
+          <t>-5,01; 3,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 45,58</t>
+          <t>-2,93; 41,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,83</t>
+          <t>-0,06; 5,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,86</t>
+          <t>-3,53; 1,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 28,11</t>
+          <t>-1,99; 29,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 30,22</t>
+          <t>-4,44; 29,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 6,96</t>
+          <t>-22,68; 7,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 17,64</t>
+          <t>-18,44; 14,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 33,85</t>
+          <t>-4,05; 34,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 19,23</t>
+          <t>-17,74; 16,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 199,59</t>
+          <t>-10,69; 152,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 25,86</t>
+          <t>-0,4; 25,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 8,37</t>
+          <t>-14,22; 7,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 124,0</t>
+          <t>-8,3; 120,35</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 8,92</t>
+          <t>-2,71; 8,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 5,98</t>
+          <t>-4,74; 6,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 9,02</t>
+          <t>-2,72; 9,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 14,96</t>
+          <t>4,55; 15,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 11,05</t>
+          <t>0,17; 10,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 4,56</t>
+          <t>-8,46; 5,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,24</t>
+          <t>2,7; 10,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,52</t>
+          <t>-1,61; 6,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 5,39</t>
+          <t>-4,41; 4,92</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 53,92</t>
+          <t>-11,78; 53,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 37,48</t>
+          <t>-19,98; 42,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 55,95</t>
+          <t>-11,91; 54,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,22; 56,51</t>
+          <t>14,29; 59,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,94; 41,96</t>
+          <t>0,98; 42,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 16,65</t>
+          <t>-26,2; 20,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,54; 47,82</t>
+          <t>9,35; 47,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 27,91</t>
+          <t>-5,68; 28,36</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 23,35</t>
+          <t>-16,52; 20,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 9,84</t>
+          <t>-2,27; 9,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 4,44</t>
+          <t>-6,23; 4,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 4,2</t>
+          <t>-7,4; 5,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,88</t>
+          <t>2,29; 9,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,1</t>
+          <t>-5,89; 1,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,36</t>
+          <t>-1,43; 6,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,41; 9,05</t>
+          <t>2,19; 8,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 0,95</t>
+          <t>-5,5; 0,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,86</t>
+          <t>-3,0; 4,0</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 103,81</t>
+          <t>-17,76; 97,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 49,84</t>
+          <t>-43,49; 47,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 45,94</t>
+          <t>-53,29; 55,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8,05; 40,57</t>
+          <t>7,73; 39,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 8,33</t>
+          <t>-20,81; 4,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 25,19</t>
+          <t>-5,14; 24,83</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,63; 40,41</t>
+          <t>8,83; 38,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 4,13</t>
+          <t>-21,56; 4,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 17,39</t>
+          <t>-12,06; 17,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,73</t>
+          <t>1,59; 5,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,19</t>
+          <t>-1,86; 2,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,93</t>
+          <t>-4,67; 1,85</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,39</t>
+          <t>3,99; 8,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,35</t>
+          <t>-1,71; 2,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 19,04</t>
+          <t>-0,76; 18,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,64</t>
+          <t>3,36; 6,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,79</t>
+          <t>-1,26; 1,69</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 11,31</t>
+          <t>-1,32; 9,64</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,7; 32,28</t>
+          <t>7,81; 32,22</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 12,24</t>
+          <t>-9,39; 11,5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 10,53</t>
+          <t>-24,03; 10,11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,01; 33,03</t>
+          <t>14,51; 33,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 9,16</t>
+          <t>-6,27; 9,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 71,34</t>
+          <t>-2,82; 70,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,44; 30,26</t>
+          <t>14,48; 29,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 8,13</t>
+          <t>-5,46; 7,74</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 49,56</t>
+          <t>-5,79; 43,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 3,82</t>
+          <t>-6,04; 4,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 4,99</t>
+          <t>-5,7; 5,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 5,6</t>
+          <t>-4,32; 5,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,53</t>
+          <t>-6,22; 7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 2,78</t>
+          <t>-10,33; 2,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 5,72</t>
+          <t>-4,79; 6,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,9</t>
+          <t>-4,35; 4,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 2,64</t>
+          <t>-5,42; 2,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 4,93</t>
+          <t>-2,85; 4,82</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 26,21</t>
+          <t>-30,89; 27,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 33,08</t>
+          <t>-28,52; 33,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 37,22</t>
+          <t>-20,79; 36,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 39,34</t>
+          <t>-24,5; 40,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 13,9</t>
+          <t>-40,16; 11,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 30,12</t>
+          <t>-18,26; 38,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 22,47</t>
+          <t>-20,58; 23,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 16,07</t>
+          <t>-25,18; 16,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 29,28</t>
+          <t>-12,99; 27,53</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 11,57</t>
+          <t>0,9; 11,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 7,36</t>
+          <t>-2,94; 7,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 6,68</t>
+          <t>-3,55; 6,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 13,41</t>
+          <t>0,05; 14,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 4,59</t>
+          <t>-8,33; 4,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 4,46</t>
+          <t>-7,44; 4,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,23</t>
+          <t>1,05; 9,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,65</t>
+          <t>-4,11; 4,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,37</t>
+          <t>-3,73; 4,1</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,6%</t>
+          <t>-2,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-1,76%</t>
+          <t>-0,27%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 100,18</t>
+          <t>4,76; 101,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 61,11</t>
+          <t>-17,21; 64,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 56,23</t>
+          <t>-20,67; 54,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 58,63</t>
+          <t>-0,04; 59,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 20,16</t>
+          <t>-28,07; 22,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 19,71</t>
+          <t>-24,74; 20,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 56,63</t>
+          <t>4,6; 53,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 26,6</t>
+          <t>-18,1; 24,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 19,28</t>
+          <t>-16,83; 21,99</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,25</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,36</t>
+          <t>2,24; 12,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 8,51</t>
+          <t>-1,38; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 7,09</t>
+          <t>-0,17; 9,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 18,29</t>
+          <t>0,54; 18,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 16,45</t>
+          <t>-4,84; 15,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 8,79</t>
+          <t>-8,34; 8,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 12,44</t>
+          <t>4,18; 12,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,52</t>
+          <t>-1,02; 8,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 5,56</t>
+          <t>-0,04; 8,79</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-17,93%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,86%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 78,71</t>
+          <t>10,56; 81,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 54,27</t>
+          <t>-6,98; 52,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,55; 41,81</t>
+          <t>-0,28; 65,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 92,46</t>
+          <t>1,67; 96,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 76,8</t>
+          <t>-15,94; 75,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 44,23</t>
+          <t>-27,41; 39,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,87; 71,08</t>
+          <t>18,13; 72,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 48,52</t>
+          <t>-4,89; 45,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 28,67</t>
+          <t>-0,17; 49,38</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,96</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>-0,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 5,89</t>
+          <t>-0,99; 6,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,48</t>
+          <t>-5,15; 1,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,97</t>
+          <t>-4,06; 2,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 8,25</t>
+          <t>-0,96; 8,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,98</t>
+          <t>-4,7; 4,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 41,18</t>
+          <t>-5,53; 3,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,72</t>
+          <t>-0,04; 5,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,6</t>
+          <t>-3,59; 1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 29,36</t>
+          <t>-3,31; 2,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-3,33%</t>
+          <t>-4,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>-4,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>-3,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 29,85</t>
+          <t>-4,24; 31,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 7,33</t>
+          <t>-22,13; 7,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 14,7</t>
+          <t>-17,31; 11,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 34,83</t>
+          <t>-3,11; 35,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 16,15</t>
+          <t>-16,41; 18,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 152,68</t>
+          <t>-18,63; 13,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 25,86</t>
+          <t>0,1; 25,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 7,22</t>
+          <t>-14,46; 7,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 120,35</t>
+          <t>-13,12; 9,27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>2,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 8,82</t>
+          <t>-2,55; 9,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 6,55</t>
+          <t>-5,06; 6,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 9,16</t>
+          <t>-4,2; 7,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 15,26</t>
+          <t>4,48; 15,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 10,92</t>
+          <t>0,28; 11,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 5,56</t>
+          <t>-1,8; 7,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 10,95</t>
+          <t>3,34; 10,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 6,62</t>
+          <t>-1,29; 6,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 4,92</t>
+          <t>-1,38; 6,03</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,45%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 53,35</t>
+          <t>-11,66; 55,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 42,25</t>
+          <t>-22,04; 40,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 54,0</t>
+          <t>-18,17; 43,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,29; 59,63</t>
+          <t>13,88; 59,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,98; 42,91</t>
+          <t>1,02; 42,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 20,3</t>
+          <t>-5,43; 29,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,35; 47,08</t>
+          <t>11,93; 45,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 28,36</t>
+          <t>-4,51; 28,26</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 20,45</t>
+          <t>-5,03; 25,31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 9,48</t>
+          <t>-2,14; 9,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 4,29</t>
+          <t>-5,64; 4,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 5,57</t>
+          <t>-5,79; 7,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,29; 9,96</t>
+          <t>2,39; 10,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,25</t>
+          <t>-5,71; 1,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,23</t>
+          <t>-1,87; 5,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,59</t>
+          <t>2,16; 8,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,79</t>
+          <t>-5,36; 0,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 4,0</t>
+          <t>-2,41; 4,32</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-20,06%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 97,96</t>
+          <t>-15,53; 100,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,49; 47,3</t>
+          <t>-40,97; 45,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 55,32</t>
+          <t>-42,46; 77,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,73; 39,82</t>
+          <t>8,39; 41,04</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 4,79</t>
+          <t>-20,07; 7,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 24,83</t>
+          <t>-6,56; 23,42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,83; 38,41</t>
+          <t>8,06; 37,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 4,22</t>
+          <t>-20,99; 4,23</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 17,91</t>
+          <t>-9,52; 19,66</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,68</t>
+          <t>1,49; 5,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,05</t>
+          <t>-1,75; 2,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,85</t>
+          <t>-1,13; 2,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,52</t>
+          <t>3,97; 8,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,51</t>
+          <t>-1,8; 2,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 18,68</t>
+          <t>-1,15; 3,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,43</t>
+          <t>3,29; 6,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,69</t>
+          <t>-1,06; 1,99</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 9,64</t>
+          <t>-0,5; 2,28</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-2,35%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>7,81; 32,22</t>
+          <t>7,58; 30,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 11,5</t>
+          <t>-8,82; 11,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 10,11</t>
+          <t>-5,65; 16,34</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,51; 33,66</t>
+          <t>14,47; 33,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,71</t>
+          <t>-6,62; 9,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 70,93</t>
+          <t>-4,1; 12,05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,48; 29,5</t>
+          <t>13,95; 28,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 7,74</t>
+          <t>-4,69; 9,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 43,24</t>
+          <t>-2,12; 10,42</t>
         </is>
       </c>
     </row>
